--- a/suivi_import_yazaki_with_anomalies.xlsx
+++ b/suivi_import_yazaki_with_anomalies.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P726"/>
+  <dimension ref="A1:Q726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,6 +510,11 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>DATE_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>COST_ANOMALY</t>
         </is>
       </c>
@@ -568,6 +573,11 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -626,6 +636,11 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -684,6 +699,11 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -742,6 +762,11 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -800,6 +825,11 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -858,6 +888,11 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -916,6 +951,11 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -974,6 +1014,11 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1032,6 +1077,11 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1090,6 +1140,11 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1148,6 +1203,11 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1206,6 +1266,11 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1264,6 +1329,11 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1322,6 +1392,11 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1380,6 +1455,11 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1438,6 +1518,11 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1496,6 +1581,11 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1554,6 +1644,11 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1612,6 +1707,11 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1670,6 +1770,11 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1728,6 +1833,11 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1786,6 +1896,11 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1844,6 +1959,11 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1902,6 +2022,11 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -1960,6 +2085,11 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2018,6 +2148,11 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2076,6 +2211,11 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2134,6 +2274,11 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2192,6 +2337,11 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2250,6 +2400,11 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2308,6 +2463,11 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2366,6 +2526,11 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2424,6 +2589,11 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2482,6 +2652,11 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2540,6 +2715,11 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2598,6 +2778,11 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2656,6 +2841,11 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2714,6 +2904,11 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2772,6 +2967,11 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2830,6 +3030,11 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2888,6 +3093,11 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -2946,6 +3156,11 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3004,6 +3219,11 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3062,6 +3282,11 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3120,6 +3345,11 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3178,6 +3408,11 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3236,6 +3471,11 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3294,6 +3534,11 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3352,6 +3597,11 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3410,6 +3660,11 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3468,6 +3723,11 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3526,6 +3786,11 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3584,6 +3849,11 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3642,6 +3912,11 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3700,6 +3975,11 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3758,6 +4038,11 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3816,6 +4101,11 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3874,6 +4164,11 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3932,6 +4227,11 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -3990,6 +4290,11 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4048,6 +4353,11 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4106,7 +4416,12 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -4164,6 +4479,11 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4222,7 +4542,12 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -4280,6 +4605,11 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4338,6 +4668,11 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4396,6 +4731,11 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4454,6 +4794,11 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4512,6 +4857,11 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4570,6 +4920,11 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4628,6 +4983,11 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4686,6 +5046,11 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4744,6 +5109,11 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -4802,6 +5172,11 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4860,6 +5235,11 @@
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4918,6 +5298,11 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -4976,6 +5361,11 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5034,6 +5424,11 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5092,6 +5487,11 @@
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5150,6 +5550,11 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5208,6 +5613,11 @@
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5266,6 +5676,11 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5324,6 +5739,11 @@
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5382,6 +5802,11 @@
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5440,7 +5865,12 @@
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -5498,6 +5928,11 @@
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5556,6 +5991,11 @@
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5614,7 +6054,12 @@
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -5672,6 +6117,11 @@
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5730,6 +6180,11 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5788,6 +6243,11 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5846,6 +6306,11 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5904,6 +6369,11 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -5962,6 +6432,11 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6020,6 +6495,11 @@
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6078,6 +6558,11 @@
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6136,6 +6621,11 @@
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6194,6 +6684,11 @@
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6252,6 +6747,11 @@
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6310,6 +6810,11 @@
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6368,6 +6873,11 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6426,6 +6936,11 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6484,6 +6999,11 @@
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6542,6 +7062,11 @@
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6600,6 +7125,11 @@
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6658,6 +7188,11 @@
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -6716,6 +7251,11 @@
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6774,6 +7314,11 @@
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6832,6 +7377,11 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6890,6 +7440,11 @@
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -6948,6 +7503,11 @@
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7006,6 +7566,11 @@
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7064,6 +7629,11 @@
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7122,6 +7692,11 @@
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7180,6 +7755,11 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7238,6 +7818,11 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7296,7 +7881,12 @@
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -7354,6 +7944,11 @@
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7412,7 +8007,12 @@
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -7470,6 +8070,11 @@
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7528,6 +8133,11 @@
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7586,6 +8196,11 @@
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7644,6 +8259,11 @@
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7702,6 +8322,11 @@
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7760,6 +8385,11 @@
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7818,6 +8448,11 @@
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7876,6 +8511,11 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7934,6 +8574,11 @@
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -7992,6 +8637,11 @@
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8050,6 +8700,11 @@
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8108,6 +8763,11 @@
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8166,6 +8826,11 @@
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8224,7 +8889,12 @@
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -8282,6 +8952,11 @@
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8340,6 +9015,11 @@
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8398,6 +9078,11 @@
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8456,6 +9141,11 @@
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8514,6 +9204,11 @@
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8572,6 +9267,11 @@
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8630,6 +9330,11 @@
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8688,6 +9393,11 @@
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8746,6 +9456,11 @@
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8804,6 +9519,11 @@
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8862,6 +9582,11 @@
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8920,6 +9645,11 @@
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -8978,6 +9708,11 @@
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9036,6 +9771,11 @@
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9094,6 +9834,11 @@
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -9152,6 +9897,11 @@
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9210,6 +9960,11 @@
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9268,6 +10023,11 @@
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9326,6 +10086,11 @@
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9384,6 +10149,11 @@
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9442,6 +10212,11 @@
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9500,6 +10275,11 @@
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9558,7 +10338,12 @@
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -9616,6 +10401,11 @@
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9674,7 +10464,12 @@
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -9732,6 +10527,11 @@
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9790,6 +10590,11 @@
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9848,6 +10653,11 @@
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9906,6 +10716,11 @@
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -9964,6 +10779,11 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10022,6 +10842,11 @@
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10080,6 +10905,11 @@
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10138,6 +10968,11 @@
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10196,6 +11031,11 @@
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10254,6 +11094,11 @@
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10312,6 +11157,11 @@
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10370,6 +11220,11 @@
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10428,6 +11283,11 @@
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10486,6 +11346,11 @@
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10544,6 +11409,11 @@
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10602,6 +11472,11 @@
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10660,6 +11535,11 @@
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10718,6 +11598,11 @@
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10776,6 +11661,11 @@
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10834,6 +11724,11 @@
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -10892,7 +11787,12 @@
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -10950,6 +11850,11 @@
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11008,7 +11913,12 @@
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -11066,6 +11976,11 @@
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11124,6 +12039,11 @@
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11182,6 +12102,11 @@
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11240,6 +12165,11 @@
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11298,6 +12228,11 @@
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11356,6 +12291,11 @@
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11414,6 +12354,11 @@
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11472,6 +12417,11 @@
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11530,6 +12480,11 @@
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11588,7 +12543,12 @@
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -11646,6 +12606,11 @@
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11704,6 +12669,11 @@
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11762,6 +12732,11 @@
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11820,6 +12795,11 @@
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11878,6 +12858,11 @@
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11936,6 +12921,11 @@
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -11994,6 +12984,11 @@
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12052,7 +13047,12 @@
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -12110,6 +13110,11 @@
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12168,6 +13173,11 @@
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12226,6 +13236,11 @@
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12284,6 +13299,11 @@
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12342,6 +13362,11 @@
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12400,6 +13425,11 @@
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12458,6 +13488,11 @@
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12516,6 +13551,11 @@
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12574,6 +13614,11 @@
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12632,6 +13677,11 @@
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12690,6 +13740,11 @@
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12748,6 +13803,11 @@
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12806,6 +13866,11 @@
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12864,6 +13929,11 @@
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12922,6 +13992,11 @@
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -12980,6 +14055,11 @@
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13038,6 +14118,11 @@
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13096,6 +14181,11 @@
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13154,6 +14244,11 @@
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13212,6 +14307,11 @@
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13270,6 +14370,11 @@
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13328,6 +14433,11 @@
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13386,6 +14496,11 @@
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13444,6 +14559,11 @@
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13502,6 +14622,11 @@
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13560,6 +14685,11 @@
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13618,6 +14748,11 @@
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13676,6 +14811,11 @@
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13734,6 +14874,11 @@
       <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13792,6 +14937,11 @@
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13850,6 +15000,11 @@
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13908,6 +15063,11 @@
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -13966,6 +15126,11 @@
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14024,6 +15189,11 @@
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14082,6 +15252,11 @@
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14140,6 +15315,11 @@
       <c r="O236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14198,6 +15378,11 @@
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14256,6 +15441,11 @@
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14314,6 +15504,11 @@
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14372,6 +15567,11 @@
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14430,6 +15630,11 @@
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14488,6 +15693,11 @@
       <c r="O242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14546,6 +15756,11 @@
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14604,6 +15819,11 @@
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14662,6 +15882,11 @@
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14720,7 +15945,12 @@
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -14778,6 +16008,11 @@
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14836,6 +16071,11 @@
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14894,6 +16134,11 @@
       <c r="O249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -14952,6 +16197,11 @@
       <c r="O250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15010,6 +16260,11 @@
       <c r="O251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15068,7 +16323,12 @@
       <c r="O252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -15126,6 +16386,11 @@
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15184,6 +16449,11 @@
       <c r="O254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15242,6 +16512,11 @@
       <c r="O255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15300,6 +16575,11 @@
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15358,6 +16638,11 @@
       <c r="O257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15416,6 +16701,11 @@
       <c r="O258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15474,6 +16764,11 @@
       <c r="O259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15532,6 +16827,11 @@
       <c r="O260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15590,6 +16890,11 @@
       <c r="O261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15648,6 +16953,11 @@
       <c r="O262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15706,6 +17016,11 @@
       <c r="O263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15764,6 +17079,11 @@
       <c r="O264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15822,6 +17142,11 @@
       <c r="O265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15880,6 +17205,11 @@
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15938,6 +17268,11 @@
       <c r="O267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -15996,6 +17331,11 @@
       <c r="O268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16054,6 +17394,11 @@
       <c r="O269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16112,6 +17457,11 @@
       <c r="O270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16170,6 +17520,11 @@
       <c r="O271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16228,6 +17583,11 @@
       <c r="O272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16286,6 +17646,11 @@
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16344,6 +17709,11 @@
       <c r="O274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16402,6 +17772,11 @@
       <c r="O275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16460,6 +17835,11 @@
       <c r="O276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16518,6 +17898,11 @@
       <c r="O277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16576,6 +17961,11 @@
       <c r="O278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16634,6 +18024,11 @@
       <c r="O279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16692,6 +18087,11 @@
       <c r="O280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16750,6 +18150,11 @@
       <c r="O281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16808,6 +18213,11 @@
       <c r="O282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16866,6 +18276,11 @@
       <c r="O283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16924,6 +18339,11 @@
       <c r="O284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
         <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -16982,6 +18402,11 @@
       <c r="O285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17040,7 +18465,12 @@
       <c r="O286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -17098,6 +18528,11 @@
       <c r="O287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17156,6 +18591,11 @@
       <c r="O288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17214,6 +18654,11 @@
       <c r="O289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17272,6 +18717,11 @@
       <c r="O290" t="inlineStr"/>
       <c r="P290" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17330,6 +18780,11 @@
       <c r="O291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -17388,6 +18843,11 @@
       <c r="O292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17446,6 +18906,11 @@
       <c r="O293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17504,6 +18969,11 @@
       <c r="O294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17562,6 +19032,11 @@
       <c r="O295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17620,6 +19095,11 @@
       <c r="O296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17678,6 +19158,11 @@
       <c r="O297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17736,6 +19221,11 @@
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17794,6 +19284,11 @@
       <c r="O299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -17852,6 +19347,11 @@
       <c r="O300" t="inlineStr"/>
       <c r="P300" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17910,6 +19410,11 @@
       <c r="O301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -17968,6 +19473,11 @@
       <c r="O302" t="inlineStr"/>
       <c r="P302" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18026,6 +19536,11 @@
       <c r="O303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18084,6 +19599,11 @@
       <c r="O304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18142,6 +19662,11 @@
       <c r="O305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18200,6 +19725,11 @@
       <c r="O306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18258,6 +19788,11 @@
       <c r="O307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18316,6 +19851,11 @@
       <c r="O308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18374,6 +19914,11 @@
       <c r="O309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18432,6 +19977,11 @@
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18490,6 +20040,11 @@
       <c r="O311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18548,6 +20103,11 @@
       <c r="O312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18606,6 +20166,11 @@
       <c r="O313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18664,6 +20229,11 @@
       <c r="O314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18722,6 +20292,11 @@
       <c r="O315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18780,6 +20355,11 @@
       <c r="O316" t="inlineStr"/>
       <c r="P316" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18838,6 +20418,11 @@
       <c r="O317" t="inlineStr"/>
       <c r="P317" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18896,6 +20481,11 @@
       <c r="O318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -18954,6 +20544,11 @@
       <c r="O319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19012,7 +20607,12 @@
       <c r="O320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -19070,6 +20670,11 @@
       <c r="O321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19128,6 +20733,11 @@
       <c r="O322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19186,6 +20796,11 @@
       <c r="O323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19244,6 +20859,11 @@
       <c r="O324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19302,6 +20922,11 @@
       <c r="O325" t="inlineStr"/>
       <c r="P325" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19360,6 +20985,11 @@
       <c r="O326" t="inlineStr"/>
       <c r="P326" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19418,6 +21048,11 @@
       <c r="O327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -19476,6 +21111,11 @@
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19534,6 +21174,11 @@
       <c r="O329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19592,7 +21237,12 @@
       <c r="O330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -19650,6 +21300,11 @@
       <c r="O331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19708,6 +21363,11 @@
       <c r="O332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19766,6 +21426,11 @@
       <c r="O333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19824,6 +21489,11 @@
       <c r="O334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19882,6 +21552,11 @@
       <c r="O335" t="inlineStr"/>
       <c r="P335" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19940,6 +21615,11 @@
       <c r="O336" t="inlineStr"/>
       <c r="P336" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -19998,6 +21678,11 @@
       <c r="O337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20056,6 +21741,11 @@
       <c r="O338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20114,6 +21804,11 @@
       <c r="O339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20172,6 +21867,11 @@
       <c r="O340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20230,6 +21930,11 @@
       <c r="O341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20288,6 +21993,11 @@
       <c r="O342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20346,6 +22056,11 @@
       <c r="O343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20404,6 +22119,11 @@
       <c r="O344" t="inlineStr"/>
       <c r="P344" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20462,6 +22182,11 @@
       <c r="O345" t="inlineStr"/>
       <c r="P345" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20520,6 +22245,11 @@
       <c r="O346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20578,6 +22308,11 @@
       <c r="O347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20636,6 +22371,11 @@
       <c r="O348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20694,6 +22434,11 @@
       <c r="O349" t="inlineStr"/>
       <c r="P349" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20752,6 +22497,11 @@
       <c r="O350" t="inlineStr"/>
       <c r="P350" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20810,6 +22560,11 @@
       <c r="O351" t="inlineStr"/>
       <c r="P351" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20868,6 +22623,11 @@
       <c r="O352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20926,6 +22686,11 @@
       <c r="O353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -20984,6 +22749,11 @@
       <c r="O354" t="inlineStr"/>
       <c r="P354" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21042,6 +22812,11 @@
       <c r="O355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21100,6 +22875,11 @@
       <c r="O356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21158,6 +22938,11 @@
       <c r="O357" t="inlineStr"/>
       <c r="P357" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21216,6 +23001,11 @@
       <c r="O358" t="inlineStr"/>
       <c r="P358" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21274,6 +23064,11 @@
       <c r="O359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21332,7 +23127,12 @@
       <c r="O360" t="inlineStr"/>
       <c r="P360" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -21390,6 +23190,11 @@
       <c r="O361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21448,6 +23253,11 @@
       <c r="O362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21506,6 +23316,11 @@
       <c r="O363" t="inlineStr"/>
       <c r="P363" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21564,6 +23379,11 @@
       <c r="O364" t="inlineStr"/>
       <c r="P364" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21622,6 +23442,11 @@
       <c r="O365" t="inlineStr"/>
       <c r="P365" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21680,6 +23505,11 @@
       <c r="O366" t="inlineStr"/>
       <c r="P366" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21738,6 +23568,11 @@
       <c r="O367" t="inlineStr"/>
       <c r="P367" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21796,6 +23631,11 @@
       <c r="O368" t="inlineStr"/>
       <c r="P368" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21854,6 +23694,11 @@
       <c r="O369" t="inlineStr"/>
       <c r="P369" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21912,6 +23757,11 @@
       <c r="O370" t="inlineStr"/>
       <c r="P370" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -21970,6 +23820,11 @@
       <c r="O371" t="inlineStr"/>
       <c r="P371" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22028,6 +23883,11 @@
       <c r="O372" t="inlineStr"/>
       <c r="P372" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22086,6 +23946,11 @@
       <c r="O373" t="inlineStr"/>
       <c r="P373" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22144,6 +24009,11 @@
       <c r="O374" t="inlineStr"/>
       <c r="P374" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22202,6 +24072,11 @@
       <c r="O375" t="inlineStr"/>
       <c r="P375" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22260,6 +24135,11 @@
       <c r="O376" t="inlineStr"/>
       <c r="P376" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22318,6 +24198,11 @@
       <c r="O377" t="inlineStr"/>
       <c r="P377" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22376,6 +24261,11 @@
       <c r="O378" t="inlineStr"/>
       <c r="P378" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22434,6 +24324,11 @@
       <c r="O379" t="inlineStr"/>
       <c r="P379" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22492,6 +24387,11 @@
       <c r="O380" t="inlineStr"/>
       <c r="P380" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22550,6 +24450,11 @@
       <c r="O381" t="inlineStr"/>
       <c r="P381" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22608,6 +24513,11 @@
       <c r="O382" t="inlineStr"/>
       <c r="P382" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22666,6 +24576,11 @@
       <c r="O383" t="inlineStr"/>
       <c r="P383" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22724,6 +24639,11 @@
       <c r="O384" t="inlineStr"/>
       <c r="P384" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22782,6 +24702,11 @@
       <c r="O385" t="inlineStr"/>
       <c r="P385" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22840,6 +24765,11 @@
       <c r="O386" t="inlineStr"/>
       <c r="P386" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -22898,7 +24828,12 @@
       <c r="O387" t="inlineStr"/>
       <c r="P387" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -22956,6 +24891,11 @@
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23014,6 +24954,11 @@
       <c r="O389" t="inlineStr"/>
       <c r="P389" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23072,6 +25017,11 @@
       <c r="O390" t="inlineStr"/>
       <c r="P390" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23130,6 +25080,11 @@
       <c r="O391" t="inlineStr"/>
       <c r="P391" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23188,6 +25143,11 @@
       <c r="O392" t="inlineStr"/>
       <c r="P392" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23246,6 +25206,11 @@
       <c r="O393" t="inlineStr"/>
       <c r="P393" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23304,6 +25269,11 @@
       <c r="O394" t="inlineStr"/>
       <c r="P394" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23362,6 +25332,11 @@
       <c r="O395" t="inlineStr"/>
       <c r="P395" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23420,6 +25395,11 @@
       <c r="O396" t="inlineStr"/>
       <c r="P396" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23478,6 +25458,11 @@
       <c r="O397" t="inlineStr"/>
       <c r="P397" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23536,6 +25521,11 @@
       <c r="O398" t="inlineStr"/>
       <c r="P398" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23594,6 +25584,11 @@
       <c r="O399" t="inlineStr"/>
       <c r="P399" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23652,6 +25647,11 @@
       <c r="O400" t="inlineStr"/>
       <c r="P400" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23710,6 +25710,11 @@
       <c r="O401" t="inlineStr"/>
       <c r="P401" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23768,6 +25773,11 @@
       <c r="O402" t="inlineStr"/>
       <c r="P402" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23826,6 +25836,11 @@
       <c r="O403" t="inlineStr"/>
       <c r="P403" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23884,6 +25899,11 @@
       <c r="O404" t="inlineStr"/>
       <c r="P404" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -23942,6 +25962,11 @@
       <c r="O405" t="inlineStr"/>
       <c r="P405" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24000,6 +26025,11 @@
       <c r="O406" t="inlineStr"/>
       <c r="P406" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24058,6 +26088,11 @@
       <c r="O407" t="inlineStr"/>
       <c r="P407" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24116,6 +26151,11 @@
       <c r="O408" t="inlineStr"/>
       <c r="P408" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24174,6 +26214,11 @@
       <c r="O409" t="inlineStr"/>
       <c r="P409" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24232,6 +26277,11 @@
       <c r="O410" t="inlineStr"/>
       <c r="P410" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24290,6 +26340,11 @@
       <c r="O411" t="inlineStr"/>
       <c r="P411" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24348,6 +26403,11 @@
       <c r="O412" t="inlineStr"/>
       <c r="P412" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24406,6 +26466,11 @@
       <c r="O413" t="inlineStr"/>
       <c r="P413" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24464,6 +26529,11 @@
       <c r="O414" t="inlineStr"/>
       <c r="P414" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24522,6 +26592,11 @@
       <c r="O415" t="inlineStr"/>
       <c r="P415" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24580,6 +26655,11 @@
       <c r="O416" t="inlineStr"/>
       <c r="P416" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24638,6 +26718,11 @@
       <c r="O417" t="inlineStr"/>
       <c r="P417" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24696,6 +26781,11 @@
       <c r="O418" t="inlineStr"/>
       <c r="P418" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24754,6 +26844,11 @@
       <c r="O419" t="inlineStr"/>
       <c r="P419" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24812,6 +26907,11 @@
       <c r="O420" t="inlineStr"/>
       <c r="P420" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24870,7 +26970,12 @@
       <c r="O421" t="inlineStr"/>
       <c r="P421" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -24928,6 +27033,11 @@
       <c r="O422" t="inlineStr"/>
       <c r="P422" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -24986,6 +27096,11 @@
       <c r="O423" t="inlineStr"/>
       <c r="P423" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25044,6 +27159,11 @@
       <c r="O424" t="inlineStr"/>
       <c r="P424" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25102,6 +27222,11 @@
       <c r="O425" t="inlineStr"/>
       <c r="P425" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25160,6 +27285,11 @@
       <c r="O426" t="inlineStr"/>
       <c r="P426" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25218,6 +27348,11 @@
       <c r="O427" t="inlineStr"/>
       <c r="P427" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25276,6 +27411,11 @@
       <c r="O428" t="inlineStr"/>
       <c r="P428" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25334,6 +27474,11 @@
       <c r="O429" t="inlineStr"/>
       <c r="P429" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25392,6 +27537,11 @@
       <c r="O430" t="inlineStr"/>
       <c r="P430" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25450,6 +27600,11 @@
       <c r="O431" t="inlineStr"/>
       <c r="P431" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25508,7 +27663,12 @@
       <c r="O432" t="inlineStr"/>
       <c r="P432" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -25566,6 +27726,11 @@
       <c r="O433" t="inlineStr"/>
       <c r="P433" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25624,6 +27789,11 @@
       <c r="O434" t="inlineStr"/>
       <c r="P434" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25682,6 +27852,11 @@
       <c r="O435" t="inlineStr"/>
       <c r="P435" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25740,6 +27915,11 @@
       <c r="O436" t="inlineStr"/>
       <c r="P436" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25798,6 +27978,11 @@
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25856,6 +28041,11 @@
       <c r="O438" t="inlineStr"/>
       <c r="P438" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25914,6 +28104,11 @@
       <c r="O439" t="inlineStr"/>
       <c r="P439" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -25972,6 +28167,11 @@
       <c r="O440" t="inlineStr"/>
       <c r="P440" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26030,6 +28230,11 @@
       <c r="O441" t="inlineStr"/>
       <c r="P441" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26088,6 +28293,11 @@
       <c r="O442" t="inlineStr"/>
       <c r="P442" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26146,6 +28356,11 @@
       <c r="O443" t="inlineStr"/>
       <c r="P443" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26204,6 +28419,11 @@
       <c r="O444" t="inlineStr"/>
       <c r="P444" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26262,6 +28482,11 @@
       <c r="O445" t="inlineStr"/>
       <c r="P445" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -26320,6 +28545,11 @@
       <c r="O446" t="inlineStr"/>
       <c r="P446" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26378,6 +28608,11 @@
       <c r="O447" t="inlineStr"/>
       <c r="P447" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26436,6 +28671,11 @@
       <c r="O448" t="inlineStr"/>
       <c r="P448" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26494,6 +28734,11 @@
       <c r="O449" t="inlineStr"/>
       <c r="P449" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26552,6 +28797,11 @@
       <c r="O450" t="inlineStr"/>
       <c r="P450" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26610,6 +28860,11 @@
       <c r="O451" t="inlineStr"/>
       <c r="P451" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26668,6 +28923,11 @@
       <c r="O452" t="inlineStr"/>
       <c r="P452" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26726,6 +28986,11 @@
       <c r="O453" t="inlineStr"/>
       <c r="P453" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26784,6 +29049,11 @@
       <c r="O454" t="inlineStr"/>
       <c r="P454" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26842,6 +29112,11 @@
       <c r="O455" t="inlineStr"/>
       <c r="P455" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26900,6 +29175,11 @@
       <c r="O456" t="inlineStr"/>
       <c r="P456" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -26958,6 +29238,11 @@
       <c r="O457" t="inlineStr"/>
       <c r="P457" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27016,6 +29301,11 @@
       <c r="O458" t="inlineStr"/>
       <c r="P458" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27074,6 +29364,11 @@
       <c r="O459" t="inlineStr"/>
       <c r="P459" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27132,6 +29427,11 @@
       <c r="O460" t="inlineStr"/>
       <c r="P460" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27190,6 +29490,11 @@
       <c r="O461" t="inlineStr"/>
       <c r="P461" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27248,6 +29553,11 @@
       <c r="O462" t="inlineStr"/>
       <c r="P462" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27306,6 +29616,11 @@
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27364,6 +29679,11 @@
       <c r="O464" t="inlineStr"/>
       <c r="P464" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27422,6 +29742,11 @@
       <c r="O465" t="inlineStr"/>
       <c r="P465" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27480,6 +29805,11 @@
       <c r="O466" t="inlineStr"/>
       <c r="P466" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27538,6 +29868,11 @@
       <c r="O467" t="inlineStr"/>
       <c r="P467" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27596,6 +29931,11 @@
       <c r="O468" t="inlineStr"/>
       <c r="P468" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27654,6 +29994,11 @@
       <c r="O469" t="inlineStr"/>
       <c r="P469" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27712,6 +30057,11 @@
       <c r="O470" t="inlineStr"/>
       <c r="P470" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27770,6 +30120,11 @@
       <c r="O471" t="inlineStr"/>
       <c r="P471" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27828,6 +30183,11 @@
       <c r="O472" t="inlineStr"/>
       <c r="P472" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27886,6 +30246,11 @@
       <c r="O473" t="inlineStr"/>
       <c r="P473" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -27944,6 +30309,11 @@
       <c r="O474" t="inlineStr"/>
       <c r="P474" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28002,6 +30372,11 @@
       <c r="O475" t="inlineStr"/>
       <c r="P475" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28060,6 +30435,11 @@
       <c r="O476" t="inlineStr"/>
       <c r="P476" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28118,6 +30498,11 @@
       <c r="O477" t="inlineStr"/>
       <c r="P477" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28176,6 +30561,11 @@
       <c r="O478" t="inlineStr"/>
       <c r="P478" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28234,6 +30624,11 @@
       <c r="O479" t="inlineStr"/>
       <c r="P479" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28292,6 +30687,11 @@
       <c r="O480" t="inlineStr"/>
       <c r="P480" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -28350,6 +30750,11 @@
       <c r="O481" t="inlineStr"/>
       <c r="P481" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28408,6 +30813,11 @@
       <c r="O482" t="inlineStr"/>
       <c r="P482" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28466,6 +30876,11 @@
       <c r="O483" t="inlineStr"/>
       <c r="P483" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28524,6 +30939,11 @@
       <c r="O484" t="inlineStr"/>
       <c r="P484" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28582,6 +31002,11 @@
       <c r="O485" t="inlineStr"/>
       <c r="P485" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28640,6 +31065,11 @@
       <c r="O486" t="inlineStr"/>
       <c r="P486" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28698,6 +31128,11 @@
       <c r="O487" t="inlineStr"/>
       <c r="P487" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28756,6 +31191,11 @@
       <c r="O488" t="inlineStr"/>
       <c r="P488" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28814,6 +31254,11 @@
       <c r="O489" t="inlineStr"/>
       <c r="P489" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28872,6 +31317,11 @@
       <c r="O490" t="inlineStr"/>
       <c r="P490" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28930,6 +31380,11 @@
       <c r="O491" t="inlineStr"/>
       <c r="P491" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -28988,6 +31443,11 @@
       <c r="O492" t="inlineStr"/>
       <c r="P492" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29046,6 +31506,11 @@
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29104,6 +31569,11 @@
       <c r="O494" t="inlineStr"/>
       <c r="P494" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -29162,6 +31632,11 @@
       <c r="O495" t="inlineStr"/>
       <c r="P495" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29220,6 +31695,11 @@
       <c r="O496" t="inlineStr"/>
       <c r="P496" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29278,6 +31758,11 @@
       <c r="O497" t="inlineStr"/>
       <c r="P497" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29336,6 +31821,11 @@
       <c r="O498" t="inlineStr"/>
       <c r="P498" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29394,6 +31884,11 @@
       <c r="O499" t="inlineStr"/>
       <c r="P499" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29452,6 +31947,11 @@
       <c r="O500" t="inlineStr"/>
       <c r="P500" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29510,6 +32010,11 @@
       <c r="O501" t="inlineStr"/>
       <c r="P501" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29568,6 +32073,11 @@
       <c r="O502" t="inlineStr"/>
       <c r="P502" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29626,6 +32136,11 @@
       <c r="O503" t="inlineStr"/>
       <c r="P503" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29684,6 +32199,11 @@
       <c r="O504" t="inlineStr"/>
       <c r="P504" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29742,6 +32262,11 @@
       <c r="O505" t="inlineStr"/>
       <c r="P505" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29800,6 +32325,11 @@
       <c r="O506" t="inlineStr"/>
       <c r="P506" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29858,7 +32388,12 @@
       <c r="O507" t="inlineStr"/>
       <c r="P507" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -29916,6 +32451,11 @@
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -29974,6 +32514,11 @@
       <c r="O509" t="inlineStr"/>
       <c r="P509" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30032,6 +32577,11 @@
       <c r="O510" t="inlineStr"/>
       <c r="P510" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30090,6 +32640,11 @@
       <c r="O511" t="inlineStr"/>
       <c r="P511" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30148,6 +32703,11 @@
       <c r="O512" t="inlineStr"/>
       <c r="P512" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -30206,6 +32766,11 @@
       <c r="O513" t="inlineStr"/>
       <c r="P513" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30264,6 +32829,11 @@
       <c r="O514" t="inlineStr"/>
       <c r="P514" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30322,6 +32892,11 @@
       <c r="O515" t="inlineStr"/>
       <c r="P515" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30380,6 +32955,11 @@
       <c r="O516" t="inlineStr"/>
       <c r="P516" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30438,6 +33018,11 @@
       <c r="O517" t="inlineStr"/>
       <c r="P517" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30496,6 +33081,11 @@
       <c r="O518" t="inlineStr"/>
       <c r="P518" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30554,7 +33144,12 @@
       <c r="O519" t="inlineStr"/>
       <c r="P519" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -30612,6 +33207,11 @@
       <c r="O520" t="inlineStr"/>
       <c r="P520" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30670,6 +33270,11 @@
       <c r="O521" t="inlineStr"/>
       <c r="P521" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30728,6 +33333,11 @@
       <c r="O522" t="inlineStr"/>
       <c r="P522" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30786,6 +33396,11 @@
       <c r="O523" t="inlineStr"/>
       <c r="P523" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30844,6 +33459,11 @@
       <c r="O524" t="inlineStr"/>
       <c r="P524" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -30902,7 +33522,12 @@
       <c r="O525" t="inlineStr"/>
       <c r="P525" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -30960,6 +33585,11 @@
       <c r="O526" t="inlineStr"/>
       <c r="P526" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31018,6 +33648,11 @@
       <c r="O527" t="inlineStr"/>
       <c r="P527" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31076,6 +33711,11 @@
       <c r="O528" t="inlineStr"/>
       <c r="P528" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31134,6 +33774,11 @@
       <c r="O529" t="inlineStr"/>
       <c r="P529" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31192,6 +33837,11 @@
       <c r="O530" t="inlineStr"/>
       <c r="P530" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31250,6 +33900,11 @@
       <c r="O531" t="inlineStr"/>
       <c r="P531" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q531" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31308,6 +33963,11 @@
       <c r="O532" t="inlineStr"/>
       <c r="P532" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q532" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31366,6 +34026,11 @@
       <c r="O533" t="inlineStr"/>
       <c r="P533" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31424,6 +34089,11 @@
       <c r="O534" t="inlineStr"/>
       <c r="P534" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q534" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31482,6 +34152,11 @@
       <c r="O535" t="inlineStr"/>
       <c r="P535" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31540,6 +34215,11 @@
       <c r="O536" t="inlineStr"/>
       <c r="P536" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q536" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31598,6 +34278,11 @@
       <c r="O537" t="inlineStr"/>
       <c r="P537" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q537" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31656,6 +34341,11 @@
       <c r="O538" t="inlineStr"/>
       <c r="P538" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31714,6 +34404,11 @@
       <c r="O539" t="inlineStr"/>
       <c r="P539" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q539" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31772,6 +34467,11 @@
       <c r="O540" t="inlineStr"/>
       <c r="P540" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31830,6 +34530,11 @@
       <c r="O541" t="inlineStr"/>
       <c r="P541" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31888,6 +34593,11 @@
       <c r="O542" t="inlineStr"/>
       <c r="P542" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q542" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -31946,6 +34656,11 @@
       <c r="O543" t="inlineStr"/>
       <c r="P543" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q543" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32004,6 +34719,11 @@
       <c r="O544" t="inlineStr"/>
       <c r="P544" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q544" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32062,6 +34782,11 @@
       <c r="O545" t="inlineStr"/>
       <c r="P545" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q545" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32120,6 +34845,11 @@
       <c r="O546" t="inlineStr"/>
       <c r="P546" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q546" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32178,6 +34908,11 @@
       <c r="O547" t="inlineStr"/>
       <c r="P547" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q547" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32236,6 +34971,11 @@
       <c r="O548" t="inlineStr"/>
       <c r="P548" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q548" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32294,6 +35034,11 @@
       <c r="O549" t="inlineStr"/>
       <c r="P549" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q549" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32352,7 +35097,12 @@
       <c r="O550" t="inlineStr"/>
       <c r="P550" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q550" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -32410,6 +35160,11 @@
       <c r="O551" t="inlineStr"/>
       <c r="P551" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q551" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32468,6 +35223,11 @@
       <c r="O552" t="inlineStr"/>
       <c r="P552" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q552" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32526,6 +35286,11 @@
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q553" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -32584,6 +35349,11 @@
       <c r="O554" t="inlineStr"/>
       <c r="P554" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q554" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32642,6 +35412,11 @@
       <c r="O555" t="inlineStr"/>
       <c r="P555" t="inlineStr">
         <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q555" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32700,6 +35475,11 @@
       <c r="O556" t="inlineStr"/>
       <c r="P556" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q556" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32758,6 +35538,11 @@
       <c r="O557" t="inlineStr"/>
       <c r="P557" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q557" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32816,6 +35601,11 @@
       <c r="O558" t="inlineStr"/>
       <c r="P558" t="inlineStr">
         <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32877,6 +35667,11 @@
         <v>-115</v>
       </c>
       <c r="P559" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q559" t="inlineStr">
         <is>
           <t>ANOMALY</t>
         </is>
@@ -32936,6 +35731,11 @@
       <c r="O560" t="inlineStr"/>
       <c r="P560" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q560" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -32994,6 +35794,11 @@
       <c r="O561" t="inlineStr"/>
       <c r="P561" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q561" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -33055,6 +35860,11 @@
         <v>-85</v>
       </c>
       <c r="P562" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q562" t="inlineStr">
         <is>
           <t>ANOMALY</t>
         </is>
@@ -33114,6 +35924,11 @@
       <c r="O563" t="inlineStr"/>
       <c r="P563" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q563" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -33176,6 +35991,11 @@
       </c>
       <c r="P564" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q564" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -33237,6 +36057,11 @@
         <v>6</v>
       </c>
       <c r="P565" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q565" t="inlineStr">
         <is>
           <t>ANOMALY</t>
         </is>
@@ -33296,6 +36121,11 @@
       <c r="O566" t="inlineStr"/>
       <c r="P566" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q566" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -33358,6 +36188,11 @@
       </c>
       <c r="P567" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q567" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -33419,6 +36254,11 @@
         <v>7</v>
       </c>
       <c r="P568" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q568" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
@@ -33478,6 +36318,11 @@
       <c r="O569" t="inlineStr"/>
       <c r="P569" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q569" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -33536,6 +36381,11 @@
       <c r="O570" t="inlineStr"/>
       <c r="P570" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q570" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -33597,6 +36447,11 @@
         <v>12</v>
       </c>
       <c r="P571" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q571" t="inlineStr">
         <is>
           <t>ANOMALY</t>
         </is>
@@ -33656,6 +36511,11 @@
       <c r="O572" t="inlineStr"/>
       <c r="P572" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q572" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -33714,6 +36574,11 @@
       <c r="O573" t="inlineStr"/>
       <c r="P573" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -33772,6 +36637,11 @@
       <c r="O574" t="inlineStr"/>
       <c r="P574" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -33834,6 +36704,11 @@
       </c>
       <c r="P575" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -33895,6 +36770,11 @@
         <v>4</v>
       </c>
       <c r="P576" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
         <is>
           <t>ANOMALY</t>
         </is>
@@ -33954,6 +36834,11 @@
       <c r="O577" t="inlineStr"/>
       <c r="P577" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -34012,6 +36897,11 @@
       <c r="O578" t="inlineStr"/>
       <c r="P578" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -34073,6 +36963,11 @@
         <v>10</v>
       </c>
       <c r="P579" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
         <is>
           <t>ANOMALY</t>
         </is>
@@ -34132,6 +37027,11 @@
       <c r="O580" t="inlineStr"/>
       <c r="P580" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -34190,6 +37090,11 @@
       <c r="O581" t="inlineStr"/>
       <c r="P581" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -34252,7 +37157,12 @@
       </c>
       <c r="P582" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -34313,6 +37223,11 @@
         <v>8</v>
       </c>
       <c r="P583" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q583" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
@@ -34372,6 +37287,11 @@
       <c r="O584" t="inlineStr"/>
       <c r="P584" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q584" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -34434,6 +37354,11 @@
       </c>
       <c r="P585" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q585" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -34496,6 +37421,11 @@
       </c>
       <c r="P586" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q586" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -34557,6 +37487,11 @@
         <v>10</v>
       </c>
       <c r="P587" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q587" t="inlineStr">
         <is>
           <t>ANOMALY</t>
         </is>
@@ -34616,6 +37551,11 @@
       <c r="O588" t="inlineStr"/>
       <c r="P588" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q588" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -34678,6 +37618,11 @@
       </c>
       <c r="P589" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q589" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -34740,6 +37685,11 @@
       </c>
       <c r="P590" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q590" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -34802,7 +37752,12 @@
       </c>
       <c r="P591" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q591" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -34864,6 +37819,11 @@
       </c>
       <c r="P592" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q592" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -34926,7 +37886,12 @@
       </c>
       <c r="P593" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q593" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -34988,7 +37953,12 @@
       </c>
       <c r="P594" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q594" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -35050,6 +38020,11 @@
       </c>
       <c r="P595" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q595" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -35112,6 +38087,11 @@
       </c>
       <c r="P596" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q596" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -35174,6 +38154,11 @@
       </c>
       <c r="P597" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q597" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -35235,6 +38220,11 @@
         <v>4</v>
       </c>
       <c r="P598" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q598" t="inlineStr">
         <is>
           <t>ANOMALY</t>
         </is>
@@ -35294,6 +38284,11 @@
       <c r="O599" t="inlineStr"/>
       <c r="P599" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q599" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -35352,6 +38347,11 @@
       <c r="O600" t="inlineStr"/>
       <c r="P600" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q600" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -35410,6 +38410,11 @@
       <c r="O601" t="inlineStr"/>
       <c r="P601" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q601" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -35468,6 +38473,11 @@
       <c r="O602" t="inlineStr"/>
       <c r="P602" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q602" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -35526,6 +38536,11 @@
       <c r="O603" t="inlineStr"/>
       <c r="P603" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q603" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -35584,6 +38599,11 @@
       <c r="O604" t="inlineStr"/>
       <c r="P604" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q604" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -35642,6 +38662,11 @@
       <c r="O605" t="inlineStr"/>
       <c r="P605" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q605" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -35700,6 +38725,11 @@
       <c r="O606" t="inlineStr"/>
       <c r="P606" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q606" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -35758,6 +38788,11 @@
       <c r="O607" t="inlineStr"/>
       <c r="P607" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q607" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -35816,6 +38851,11 @@
       <c r="O608" t="inlineStr"/>
       <c r="P608" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q608" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -35874,6 +38914,11 @@
       <c r="O609" t="inlineStr"/>
       <c r="P609" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q609" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -35932,6 +38977,11 @@
       <c r="O610" t="inlineStr"/>
       <c r="P610" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q610" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -35990,6 +39040,11 @@
       <c r="O611" t="inlineStr"/>
       <c r="P611" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q611" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36048,6 +39103,11 @@
       <c r="O612" t="inlineStr"/>
       <c r="P612" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q612" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36106,7 +39166,12 @@
       <c r="O613" t="inlineStr"/>
       <c r="P613" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q613" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -36164,6 +39229,11 @@
       <c r="O614" t="inlineStr"/>
       <c r="P614" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q614" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -36222,6 +39292,11 @@
       <c r="O615" t="inlineStr"/>
       <c r="P615" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q615" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36280,6 +39355,11 @@
       <c r="O616" t="inlineStr"/>
       <c r="P616" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q616" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36338,6 +39418,11 @@
       <c r="O617" t="inlineStr"/>
       <c r="P617" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q617" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36396,6 +39481,11 @@
       <c r="O618" t="inlineStr"/>
       <c r="P618" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q618" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36454,6 +39544,11 @@
       <c r="O619" t="inlineStr"/>
       <c r="P619" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q619" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36512,6 +39607,11 @@
       <c r="O620" t="inlineStr"/>
       <c r="P620" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q620" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36570,6 +39670,11 @@
       <c r="O621" t="inlineStr"/>
       <c r="P621" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q621" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36628,6 +39733,11 @@
       <c r="O622" t="inlineStr"/>
       <c r="P622" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q622" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36686,6 +39796,11 @@
       <c r="O623" t="inlineStr"/>
       <c r="P623" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q623" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36744,6 +39859,11 @@
       <c r="O624" t="inlineStr"/>
       <c r="P624" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q624" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36802,6 +39922,11 @@
       <c r="O625" t="inlineStr"/>
       <c r="P625" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q625" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36860,6 +39985,11 @@
       <c r="O626" t="inlineStr"/>
       <c r="P626" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q626" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36918,6 +40048,11 @@
       <c r="O627" t="inlineStr"/>
       <c r="P627" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q627" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -36976,6 +40111,11 @@
       <c r="O628" t="inlineStr"/>
       <c r="P628" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q628" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37034,7 +40174,12 @@
       <c r="O629" t="inlineStr"/>
       <c r="P629" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q629" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -37092,6 +40237,11 @@
       <c r="O630" t="inlineStr"/>
       <c r="P630" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q630" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37150,6 +40300,11 @@
       <c r="O631" t="inlineStr"/>
       <c r="P631" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q631" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37208,6 +40363,11 @@
       <c r="O632" t="inlineStr"/>
       <c r="P632" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q632" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37266,6 +40426,11 @@
       <c r="O633" t="inlineStr"/>
       <c r="P633" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q633" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37324,6 +40489,11 @@
       <c r="O634" t="inlineStr"/>
       <c r="P634" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q634" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37382,6 +40552,11 @@
       <c r="O635" t="inlineStr"/>
       <c r="P635" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q635" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37440,6 +40615,11 @@
       <c r="O636" t="inlineStr"/>
       <c r="P636" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q636" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37498,6 +40678,11 @@
       <c r="O637" t="inlineStr"/>
       <c r="P637" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q637" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37556,6 +40741,11 @@
       <c r="O638" t="inlineStr"/>
       <c r="P638" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q638" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37614,6 +40804,11 @@
       <c r="O639" t="inlineStr"/>
       <c r="P639" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q639" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37672,6 +40867,11 @@
       <c r="O640" t="inlineStr"/>
       <c r="P640" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q640" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37730,6 +40930,11 @@
       <c r="O641" t="inlineStr"/>
       <c r="P641" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q641" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37788,6 +40993,11 @@
       <c r="O642" t="inlineStr"/>
       <c r="P642" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q642" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37846,6 +41056,11 @@
       <c r="O643" t="inlineStr"/>
       <c r="P643" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q643" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37904,6 +41119,11 @@
       <c r="O644" t="inlineStr"/>
       <c r="P644" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q644" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -37962,6 +41182,11 @@
       <c r="O645" t="inlineStr"/>
       <c r="P645" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q645" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -38020,7 +41245,12 @@
       <c r="O646" t="inlineStr"/>
       <c r="P646" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q646" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -38078,6 +41308,11 @@
       <c r="O647" t="inlineStr"/>
       <c r="P647" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q647" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -38136,6 +41371,11 @@
       <c r="O648" t="inlineStr"/>
       <c r="P648" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q648" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -38194,6 +41434,11 @@
       <c r="O649" t="inlineStr"/>
       <c r="P649" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q649" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -38252,6 +41497,11 @@
       <c r="O650" t="inlineStr"/>
       <c r="P650" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q650" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -38310,6 +41560,11 @@
       <c r="O651" t="inlineStr"/>
       <c r="P651" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q651" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -38368,6 +41623,11 @@
       <c r="O652" t="inlineStr"/>
       <c r="P652" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q652" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -38426,6 +41686,11 @@
       <c r="O653" t="inlineStr"/>
       <c r="P653" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q653" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -38484,6 +41749,11 @@
       <c r="O654" t="inlineStr"/>
       <c r="P654" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q654" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -38542,6 +41812,11 @@
       <c r="O655" t="inlineStr"/>
       <c r="P655" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q655" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -38600,6 +41875,11 @@
       <c r="O656" t="inlineStr"/>
       <c r="P656" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q656" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -38658,6 +41938,11 @@
       <c r="O657" t="inlineStr"/>
       <c r="P657" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q657" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -38716,6 +42001,11 @@
       <c r="O658" t="inlineStr"/>
       <c r="P658" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q658" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -38774,6 +42064,11 @@
       <c r="O659" t="inlineStr"/>
       <c r="P659" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q659" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -38832,6 +42127,11 @@
       <c r="O660" t="inlineStr"/>
       <c r="P660" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q660" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -38890,6 +42190,11 @@
       <c r="O661" t="inlineStr"/>
       <c r="P661" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q661" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -38948,6 +42253,11 @@
       <c r="O662" t="inlineStr"/>
       <c r="P662" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q662" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39006,6 +42316,11 @@
       <c r="O663" t="inlineStr"/>
       <c r="P663" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q663" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39064,6 +42379,11 @@
       <c r="O664" t="inlineStr"/>
       <c r="P664" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q664" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39122,6 +42442,11 @@
       <c r="O665" t="inlineStr"/>
       <c r="P665" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q665" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39180,6 +42505,11 @@
       <c r="O666" t="inlineStr"/>
       <c r="P666" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q666" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39238,6 +42568,11 @@
       <c r="O667" t="inlineStr"/>
       <c r="P667" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q667" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39296,6 +42631,11 @@
       <c r="O668" t="inlineStr"/>
       <c r="P668" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q668" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39354,6 +42694,11 @@
       <c r="O669" t="inlineStr"/>
       <c r="P669" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q669" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39412,6 +42757,11 @@
       <c r="O670" t="inlineStr"/>
       <c r="P670" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q670" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39470,6 +42820,11 @@
       <c r="O671" t="inlineStr"/>
       <c r="P671" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q671" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39528,7 +42883,12 @@
       <c r="O672" t="inlineStr"/>
       <c r="P672" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q672" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -39586,6 +42946,11 @@
       <c r="O673" t="inlineStr"/>
       <c r="P673" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q673" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39644,6 +43009,11 @@
       <c r="O674" t="inlineStr"/>
       <c r="P674" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q674" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39702,6 +43072,11 @@
       <c r="O675" t="inlineStr"/>
       <c r="P675" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q675" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39760,6 +43135,11 @@
       <c r="O676" t="inlineStr"/>
       <c r="P676" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q676" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39818,6 +43198,11 @@
       <c r="O677" t="inlineStr"/>
       <c r="P677" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q677" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39876,6 +43261,11 @@
       <c r="O678" t="inlineStr"/>
       <c r="P678" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q678" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39934,6 +43324,11 @@
       <c r="O679" t="inlineStr"/>
       <c r="P679" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q679" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -39992,6 +43387,11 @@
       <c r="O680" t="inlineStr"/>
       <c r="P680" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q680" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40050,6 +43450,11 @@
       <c r="O681" t="inlineStr"/>
       <c r="P681" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q681" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40108,6 +43513,11 @@
       <c r="O682" t="inlineStr"/>
       <c r="P682" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q682" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40166,6 +43576,11 @@
       <c r="O683" t="inlineStr"/>
       <c r="P683" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q683" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40224,6 +43639,11 @@
       <c r="O684" t="inlineStr"/>
       <c r="P684" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q684" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40282,6 +43702,11 @@
       <c r="O685" t="inlineStr"/>
       <c r="P685" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q685" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40340,6 +43765,11 @@
       <c r="O686" t="inlineStr"/>
       <c r="P686" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q686" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40398,6 +43828,11 @@
       <c r="O687" t="inlineStr"/>
       <c r="P687" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q687" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40456,6 +43891,11 @@
       <c r="O688" t="inlineStr"/>
       <c r="P688" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q688" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40514,7 +43954,12 @@
       <c r="O689" t="inlineStr"/>
       <c r="P689" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q689" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -40572,6 +44017,11 @@
       <c r="O690" t="inlineStr"/>
       <c r="P690" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q690" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40630,7 +44080,12 @@
       <c r="O691" t="inlineStr"/>
       <c r="P691" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q691" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
         </is>
       </c>
     </row>
@@ -40688,6 +44143,11 @@
       <c r="O692" t="inlineStr"/>
       <c r="P692" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q692" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40746,6 +44206,11 @@
       <c r="O693" t="inlineStr"/>
       <c r="P693" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q693" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40804,6 +44269,11 @@
       <c r="O694" t="inlineStr"/>
       <c r="P694" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q694" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -40862,6 +44332,11 @@
       <c r="O695" t="inlineStr"/>
       <c r="P695" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q695" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40920,6 +44395,11 @@
       <c r="O696" t="inlineStr"/>
       <c r="P696" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q696" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -40978,6 +44458,11 @@
       <c r="O697" t="inlineStr"/>
       <c r="P697" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q697" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41036,6 +44521,11 @@
       <c r="O698" t="inlineStr"/>
       <c r="P698" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q698" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41094,6 +44584,11 @@
       <c r="O699" t="inlineStr"/>
       <c r="P699" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q699" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41152,6 +44647,11 @@
       <c r="O700" t="inlineStr"/>
       <c r="P700" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q700" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41210,6 +44710,11 @@
       <c r="O701" t="inlineStr"/>
       <c r="P701" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q701" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -41268,6 +44773,11 @@
       <c r="O702" t="inlineStr"/>
       <c r="P702" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q702" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41326,6 +44836,11 @@
       <c r="O703" t="inlineStr"/>
       <c r="P703" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q703" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41384,6 +44899,11 @@
       <c r="O704" t="inlineStr"/>
       <c r="P704" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q704" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41442,6 +44962,11 @@
       <c r="O705" t="inlineStr"/>
       <c r="P705" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q705" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41500,6 +45025,11 @@
       <c r="O706" t="inlineStr"/>
       <c r="P706" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q706" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41558,6 +45088,11 @@
       <c r="O707" t="inlineStr"/>
       <c r="P707" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q707" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41616,6 +45151,11 @@
       <c r="O708" t="inlineStr"/>
       <c r="P708" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q708" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41674,6 +45214,11 @@
       <c r="O709" t="inlineStr"/>
       <c r="P709" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q709" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41732,6 +45277,11 @@
       <c r="O710" t="inlineStr"/>
       <c r="P710" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q710" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41790,6 +45340,11 @@
       <c r="O711" t="inlineStr"/>
       <c r="P711" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q711" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41848,6 +45403,11 @@
       <c r="O712" t="inlineStr"/>
       <c r="P712" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q712" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41906,6 +45466,11 @@
       <c r="O713" t="inlineStr"/>
       <c r="P713" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q713" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -41964,6 +45529,11 @@
       <c r="O714" t="inlineStr"/>
       <c r="P714" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q714" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -42022,6 +45592,11 @@
       <c r="O715" t="inlineStr"/>
       <c r="P715" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q715" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -42080,6 +45655,11 @@
       <c r="O716" t="inlineStr"/>
       <c r="P716" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q716" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -42138,6 +45718,11 @@
       <c r="O717" t="inlineStr"/>
       <c r="P717" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q717" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -42196,6 +45781,11 @@
       <c r="O718" t="inlineStr"/>
       <c r="P718" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q718" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -42254,6 +45844,11 @@
       <c r="O719" t="inlineStr"/>
       <c r="P719" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q719" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -42312,6 +45907,11 @@
       <c r="O720" t="inlineStr"/>
       <c r="P720" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q720" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -42370,6 +45970,11 @@
       <c r="O721" t="inlineStr"/>
       <c r="P721" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q721" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -42428,6 +46033,11 @@
       <c r="O722" t="inlineStr"/>
       <c r="P722" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q722" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -42486,6 +46096,11 @@
       <c r="O723" t="inlineStr"/>
       <c r="P723" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q723" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -42544,6 +46159,11 @@
       <c r="O724" t="inlineStr"/>
       <c r="P724" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q724" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
@@ -42602,6 +46222,11 @@
       <c r="O725" t="inlineStr"/>
       <c r="P725" t="inlineStr">
         <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q725" t="inlineStr">
+        <is>
           <t>NORMAL</t>
         </is>
       </c>
@@ -42659,6 +46284,11 @@
       </c>
       <c r="O726" t="inlineStr"/>
       <c r="P726" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="Q726" t="inlineStr">
         <is>
           <t>ANOMALY</t>
         </is>
